--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 3.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 3.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Keuangan 3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Keuangan\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1AE70F-8765-4829-9378-D9498C47A2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="9" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
 </workbook>
 </file>
 
@@ -137,7 +136,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -260,7 +259,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="7">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -338,13 +337,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -390,13 +402,61 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -412,34 +472,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -554,23 +587,6 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -606,23 +622,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -798,7 +797,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868AE351-5EAC-4760-9262-7B6887FEAB8D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
@@ -824,13 +823,13 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="28" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="1"/>
@@ -844,21 +843,21 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="35" t="s">
+      <c r="B2" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="1"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="29"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="35" t="s">
+      <c r="J2" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
@@ -924,9 +923,18 @@
       <c r="E4" s="8">
         <v>85000</v>
       </c>
-      <c r="F4" s="21"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
+      <c r="F4" s="30">
+        <f>C4*E4</f>
+        <v>8500</v>
+      </c>
+      <c r="G4" s="22">
+        <f>E4+F4</f>
+        <v>93500</v>
+      </c>
+      <c r="H4" s="22">
+        <f>F4*D4</f>
+        <v>850000</v>
+      </c>
       <c r="I4" s="1"/>
       <c r="J4" s="5">
         <v>1</v>
@@ -934,31 +942,52 @@
       <c r="K4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="10"/>
+      <c r="L4" s="10">
+        <f>VLOOKUP(K4,$B$3:$H$8,6,FALSE)</f>
+        <v>93500</v>
+      </c>
       <c r="M4" s="9">
         <v>11</v>
       </c>
-      <c r="N4" s="10"/>
-      <c r="O4" s="10"/>
-      <c r="P4" s="10"/>
+      <c r="N4" s="10">
+        <f>L4*M4</f>
+        <v>1028500</v>
+      </c>
+      <c r="O4" s="10">
+        <f>IF(M4&gt;10,N4*0.025,0)</f>
+        <v>25712.5</v>
+      </c>
+      <c r="P4" s="10">
+        <f>N4-O4</f>
+        <v>1002787.5</v>
+      </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="24" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="7">
+      <c r="C5" s="25">
         <v>0.15</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5" s="26">
         <v>100</v>
       </c>
-      <c r="E5" s="8">
+      <c r="E5" s="27">
         <v>75000</v>
       </c>
-      <c r="F5" s="22"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
+      <c r="F5" s="31">
+        <f t="shared" ref="F5:F8" si="0">C5*E5</f>
+        <v>11250</v>
+      </c>
+      <c r="G5" s="22">
+        <f t="shared" ref="G5:G8" si="1">E5+F5</f>
+        <v>86250</v>
+      </c>
+      <c r="H5" s="22">
+        <f t="shared" ref="H5:H8" si="2">F5*D5</f>
+        <v>1125000</v>
+      </c>
       <c r="I5" s="1"/>
       <c r="J5" s="5">
         <v>2</v>
@@ -966,13 +995,25 @@
       <c r="K5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="10"/>
+      <c r="L5" s="10">
+        <f t="shared" ref="L5:L7" si="3">VLOOKUP(K5,$B$3:$H$8,6,FALSE)</f>
+        <v>86250</v>
+      </c>
       <c r="M5" s="9">
         <v>10</v>
       </c>
-      <c r="N5" s="10"/>
-      <c r="O5" s="10"/>
-      <c r="P5" s="10"/>
+      <c r="N5" s="10">
+        <f t="shared" ref="N5:N7" si="4">L5*M5</f>
+        <v>862500</v>
+      </c>
+      <c r="O5" s="10">
+        <f t="shared" ref="O5:O7" si="5">IF(M5&gt;10,N5*0.025,0)</f>
+        <v>0</v>
+      </c>
+      <c r="P5" s="10">
+        <f t="shared" ref="P5:P7" si="6">N5-O5</f>
+        <v>862500</v>
+      </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
@@ -988,9 +1029,18 @@
       <c r="E6" s="8">
         <v>120000</v>
       </c>
-      <c r="F6" s="22"/>
-      <c r="G6" s="19"/>
-      <c r="H6" s="19"/>
+      <c r="F6" s="31">
+        <f t="shared" si="0"/>
+        <v>14400</v>
+      </c>
+      <c r="G6" s="22">
+        <f t="shared" si="1"/>
+        <v>134400</v>
+      </c>
+      <c r="H6" s="22">
+        <f t="shared" si="2"/>
+        <v>1440000</v>
+      </c>
       <c r="I6" s="1"/>
       <c r="J6" s="5">
         <v>3</v>
@@ -998,13 +1048,25 @@
       <c r="K6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="10"/>
+      <c r="L6" s="10">
+        <f t="shared" si="3"/>
+        <v>134400</v>
+      </c>
       <c r="M6" s="9">
         <v>17</v>
       </c>
-      <c r="N6" s="10"/>
-      <c r="O6" s="10"/>
-      <c r="P6" s="10"/>
+      <c r="N6" s="10">
+        <f t="shared" si="4"/>
+        <v>2284800</v>
+      </c>
+      <c r="O6" s="10">
+        <f t="shared" si="5"/>
+        <v>57120</v>
+      </c>
+      <c r="P6" s="10">
+        <f t="shared" si="6"/>
+        <v>2227680</v>
+      </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
@@ -1020,9 +1082,18 @@
       <c r="E7" s="8">
         <v>65000</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="19"/>
-      <c r="H7" s="19"/>
+      <c r="F7" s="31">
+        <f t="shared" si="0"/>
+        <v>8450</v>
+      </c>
+      <c r="G7" s="22">
+        <f t="shared" si="1"/>
+        <v>73450</v>
+      </c>
+      <c r="H7" s="22">
+        <f t="shared" si="2"/>
+        <v>845000</v>
+      </c>
       <c r="I7" s="1"/>
       <c r="J7" s="5">
         <v>4</v>
@@ -1030,13 +1101,25 @@
       <c r="K7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="10"/>
+      <c r="L7" s="10">
+        <f t="shared" si="3"/>
+        <v>73450</v>
+      </c>
       <c r="M7" s="9">
         <v>14</v>
       </c>
-      <c r="N7" s="10"/>
-      <c r="O7" s="10"/>
-      <c r="P7" s="10"/>
+      <c r="N7" s="10">
+        <f t="shared" si="4"/>
+        <v>1028300</v>
+      </c>
+      <c r="O7" s="10">
+        <f t="shared" si="5"/>
+        <v>25707.5</v>
+      </c>
+      <c r="P7" s="10">
+        <f t="shared" si="6"/>
+        <v>1002592.5</v>
+      </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
@@ -1052,28 +1135,43 @@
       <c r="E8" s="8">
         <v>84500</v>
       </c>
-      <c r="F8" s="22"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
+      <c r="F8" s="23">
+        <f t="shared" si="0"/>
+        <v>8450</v>
+      </c>
+      <c r="G8" s="22">
+        <f t="shared" si="1"/>
+        <v>92950</v>
+      </c>
+      <c r="H8" s="22">
+        <f t="shared" si="2"/>
+        <v>845000</v>
+      </c>
       <c r="I8" s="1"/>
-      <c r="J8" s="24" t="s">
+      <c r="J8" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="25"/>
-      <c r="L8" s="25"/>
-      <c r="M8" s="25"/>
-      <c r="N8" s="25"/>
-      <c r="O8" s="26"/>
-      <c r="P8" s="20"/>
+      <c r="K8" s="45"/>
+      <c r="L8" s="45"/>
+      <c r="M8" s="45"/>
+      <c r="N8" s="45"/>
+      <c r="O8" s="46"/>
+      <c r="P8" s="20">
+        <f>SUM(P4:P7)</f>
+        <v>5095560</v>
+      </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="47" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="42">
+        <f>SUM(H4:H8)</f>
+        <v>5105000</v>
+      </c>
+      <c r="E9" s="43"/>
       <c r="I9" s="1"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
@@ -1085,12 +1183,15 @@
     </row>
     <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="29" t="s">
+      <c r="B10" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="30"/>
-      <c r="D10" s="23"/>
-      <c r="E10" s="23"/>
+      <c r="C10" s="35"/>
+      <c r="D10" s="42">
+        <f>AVERAGE(H4:H8)</f>
+        <v>1021000</v>
+      </c>
+      <c r="E10" s="43"/>
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
@@ -1102,21 +1203,24 @@
       <c r="L10" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="31" t="s">
+      <c r="M10" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="31"/>
+      <c r="N10" s="49"/>
       <c r="O10" s="1"/>
       <c r="P10" s="1"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="29" t="s">
+      <c r="B11" s="34" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="32"/>
+      <c r="C11" s="35"/>
+      <c r="D11" s="32">
+        <f>MAX(H4:H8)</f>
+        <v>1440000</v>
+      </c>
+      <c r="E11" s="33"/>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
       <c r="H11" s="17"/>
@@ -1124,18 +1228,27 @@
       <c r="K11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="19"/>
-      <c r="M11" s="23"/>
-      <c r="N11" s="23"/>
+      <c r="L11" s="19">
+        <f>D4-M4</f>
+        <v>89</v>
+      </c>
+      <c r="M11" s="42">
+        <f>F4*M4</f>
+        <v>93500</v>
+      </c>
+      <c r="N11" s="43"/>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="29" t="s">
+      <c r="B12" s="34" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
+      <c r="C12" s="35"/>
+      <c r="D12" s="32">
+        <f>MIN(H4:H8)</f>
+        <v>845000</v>
+      </c>
+      <c r="E12" s="33"/>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="17"/>
@@ -1143,73 +1256,90 @@
       <c r="K12" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="19"/>
-      <c r="M12" s="23"/>
-      <c r="N12" s="23"/>
+      <c r="L12" s="21">
+        <f t="shared" ref="L12:L15" si="7">D5-M5</f>
+        <v>90</v>
+      </c>
+      <c r="M12" s="42">
+        <f t="shared" ref="M12:M15" si="8">F5*M5</f>
+        <v>112500</v>
+      </c>
+      <c r="N12" s="43"/>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="33" t="s">
+      <c r="B13" s="36" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="33"/>
-      <c r="D13" s="33"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" s="37"/>
+      <c r="G13" s="37"/>
+      <c r="H13" s="37"/>
       <c r="I13" s="1"/>
       <c r="K13" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="L13" s="19"/>
-      <c r="M13" s="23"/>
-      <c r="N13" s="23"/>
+      <c r="L13" s="21">
+        <f t="shared" si="7"/>
+        <v>83</v>
+      </c>
+      <c r="M13" s="42">
+        <f t="shared" si="8"/>
+        <v>244800</v>
+      </c>
+      <c r="N13" s="43"/>
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B14" s="34"/>
-      <c r="C14" s="34"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="34"/>
-      <c r="F14" s="34"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="34"/>
+      <c r="B14" s="37"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="37"/>
+      <c r="E14" s="37"/>
+      <c r="F14" s="37"/>
+      <c r="G14" s="37"/>
+      <c r="H14" s="37"/>
       <c r="K14" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="19"/>
-      <c r="M14" s="23"/>
-      <c r="N14" s="23"/>
+      <c r="L14" s="21">
+        <f t="shared" si="7"/>
+        <v>86</v>
+      </c>
+      <c r="M14" s="42">
+        <f t="shared" si="8"/>
+        <v>118300</v>
+      </c>
+      <c r="N14" s="43"/>
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="K15" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="L15" s="19"/>
-      <c r="M15" s="23"/>
-      <c r="N15" s="23"/>
+      <c r="L15" s="21">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+      <c r="M15" s="42">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="N15" s="43"/>
     </row>
     <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E16" s="36" t="s">
+      <c r="E16" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="36"/>
-      <c r="G16" s="37" t="s">
+      <c r="F16" s="40"/>
+      <c r="G16" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="38"/>
-      <c r="I16" s="38"/>
-      <c r="J16" s="38"/>
+      <c r="H16" s="39"/>
+      <c r="I16" s="39"/>
+      <c r="J16" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="20">
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="E16:F16"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
     <mergeCell ref="M14:N14"/>
     <mergeCell ref="M15:N15"/>
     <mergeCell ref="J8:O8"/>
@@ -1219,13 +1349,20 @@
     <mergeCell ref="D10:E10"/>
     <mergeCell ref="M10:N10"/>
     <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:H14"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="E16:F16"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G16" r:id="rId1" xr:uid="{209A80AC-3FCB-45C1-B278-3C422403E500}"/>
+    <hyperlink ref="G16" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>

--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 3.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 3.xlsx
@@ -14,6 +14,9 @@
   <sheets>
     <sheet name="Soal" sheetId="9" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Soal!$K$10:$O$16</definedName>
+  </definedNames>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
@@ -421,18 +424,45 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -446,33 +476,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -801,7 +804,7 @@
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:Q16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="11" customWidth="1"/>
@@ -814,14 +817,14 @@
     <col min="10" max="10" width="4.85546875" style="11" customWidth="1"/>
     <col min="11" max="11" width="9.7109375" style="11" customWidth="1"/>
     <col min="12" max="12" width="11.42578125" style="11" customWidth="1"/>
-    <col min="13" max="13" width="9" style="11" customWidth="1"/>
-    <col min="14" max="14" width="16" style="11" customWidth="1"/>
-    <col min="15" max="15" width="13.7109375" style="11" customWidth="1"/>
-    <col min="16" max="16" width="17.140625" style="11" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="11"/>
+    <col min="13" max="14" width="9" style="11" customWidth="1"/>
+    <col min="15" max="15" width="16" style="11" customWidth="1"/>
+    <col min="16" max="16" width="13.7109375" style="11" customWidth="1"/>
+    <col min="17" max="17" width="17.140625" style="11" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="28" t="s">
         <v>20</v>
@@ -840,30 +843,32 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q1" s="1"/>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="42" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
+      <c r="C2" s="42"/>
+      <c r="D2" s="42"/>
+      <c r="E2" s="42"/>
       <c r="F2" s="29"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="41" t="s">
+      <c r="J2" s="42" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
+      <c r="K2" s="42"/>
+      <c r="L2" s="42"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-    </row>
-    <row r="3" spans="1:16" ht="33" x14ac:dyDescent="0.3">
+      <c r="Q2" s="1"/>
+    </row>
+    <row r="3" spans="1:17" ht="33" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="3" t="s">
         <v>28</v>
@@ -899,17 +904,18 @@
       <c r="M3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="4"/>
+      <c r="O3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="P3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="Q3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="6" t="s">
         <v>1</v>
@@ -949,20 +955,21 @@
       <c r="M4" s="9">
         <v>11</v>
       </c>
-      <c r="N4" s="10">
+      <c r="N4" s="9"/>
+      <c r="O4" s="10">
         <f>L4*M4</f>
         <v>1028500</v>
       </c>
-      <c r="O4" s="10">
-        <f>IF(M4&gt;10,N4*0.025,0)</f>
+      <c r="P4" s="10">
+        <f>IF(M4&gt;10,O4*0.025,0)</f>
         <v>25712.5</v>
       </c>
-      <c r="P4" s="10">
-        <f>N4-O4</f>
+      <c r="Q4" s="10">
+        <f>O4-P4</f>
         <v>1002787.5</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="24" t="s">
         <v>2</v>
@@ -1002,20 +1009,21 @@
       <c r="M5" s="9">
         <v>10</v>
       </c>
-      <c r="N5" s="10">
-        <f t="shared" ref="N5:N7" si="4">L5*M5</f>
+      <c r="N5" s="9"/>
+      <c r="O5" s="10">
+        <f t="shared" ref="O5:O7" si="4">L5*M5</f>
         <v>862500</v>
       </c>
-      <c r="O5" s="10">
-        <f t="shared" ref="O5:O7" si="5">IF(M5&gt;10,N5*0.025,0)</f>
+      <c r="P5" s="10">
+        <f t="shared" ref="P5:P7" si="5">IF(M5&gt;10,O5*0.025,0)</f>
         <v>0</v>
       </c>
-      <c r="P5" s="10">
-        <f t="shared" ref="P5:P7" si="6">N5-O5</f>
+      <c r="Q5" s="10">
+        <f t="shared" ref="Q5:Q7" si="6">O5-P5</f>
         <v>862500</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="6" t="s">
         <v>3</v>
@@ -1055,20 +1063,21 @@
       <c r="M6" s="9">
         <v>17</v>
       </c>
-      <c r="N6" s="10">
+      <c r="N6" s="9"/>
+      <c r="O6" s="10">
         <f t="shared" si="4"/>
         <v>2284800</v>
       </c>
-      <c r="O6" s="10">
+      <c r="P6" s="10">
         <f t="shared" si="5"/>
         <v>57120</v>
       </c>
-      <c r="P6" s="10">
+      <c r="Q6" s="10">
         <f t="shared" si="6"/>
         <v>2227680</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="6" t="s">
         <v>4</v>
@@ -1108,20 +1117,21 @@
       <c r="M7" s="9">
         <v>14</v>
       </c>
-      <c r="N7" s="10">
+      <c r="N7" s="9"/>
+      <c r="O7" s="10">
         <f t="shared" si="4"/>
         <v>1028300</v>
       </c>
-      <c r="O7" s="10">
+      <c r="P7" s="10">
         <f t="shared" si="5"/>
         <v>25707.5</v>
       </c>
-      <c r="P7" s="10">
+      <c r="Q7" s="10">
         <f t="shared" si="6"/>
         <v>1002592.5</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -1148,50 +1158,52 @@
         <v>845000</v>
       </c>
       <c r="I8" s="1"/>
-      <c r="J8" s="44" t="s">
+      <c r="J8" s="34" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="45"/>
-      <c r="L8" s="45"/>
-      <c r="M8" s="45"/>
-      <c r="N8" s="45"/>
-      <c r="O8" s="46"/>
-      <c r="P8" s="20">
-        <f>SUM(P4:P7)</f>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="36"/>
+      <c r="Q8" s="20">
+        <f>SUM(Q4:Q7)</f>
         <v>5095560</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="47" t="s">
+      <c r="B9" s="37" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="48"/>
-      <c r="D9" s="42">
+      <c r="C9" s="38"/>
+      <c r="D9" s="32">
         <f>SUM(H4:H8)</f>
         <v>5105000</v>
       </c>
-      <c r="E9" s="43"/>
+      <c r="E9" s="33"/>
       <c r="I9" s="1"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="12"/>
-      <c r="P9" s="14"/>
-    </row>
-    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O9" s="13"/>
+      <c r="P9" s="12"/>
+      <c r="Q9" s="14"/>
+    </row>
+    <row r="10" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="34" t="s">
+      <c r="B10" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="35"/>
-      <c r="D10" s="42">
+      <c r="C10" s="40"/>
+      <c r="D10" s="32">
         <f>AVERAGE(H4:H8)</f>
         <v>1021000</v>
       </c>
-      <c r="E10" s="43"/>
+      <c r="E10" s="33"/>
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
@@ -1203,24 +1215,25 @@
       <c r="L10" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="49" t="s">
+      <c r="M10" s="41" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="49"/>
-      <c r="O10" s="1"/>
+      <c r="N10" s="41"/>
+      <c r="O10" s="41"/>
       <c r="P10" s="1"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="Q10" s="1"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="34" t="s">
+      <c r="B11" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35"/>
-      <c r="D11" s="32">
+      <c r="C11" s="40"/>
+      <c r="D11" s="43">
         <f>MAX(H4:H8)</f>
         <v>1440000</v>
       </c>
-      <c r="E11" s="33"/>
+      <c r="E11" s="44"/>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
       <c r="H11" s="17"/>
@@ -1232,23 +1245,24 @@
         <f>D4-M4</f>
         <v>89</v>
       </c>
-      <c r="M11" s="42">
+      <c r="M11" s="32">
         <f>F4*M4</f>
         <v>93500</v>
       </c>
-      <c r="N11" s="43"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N11" s="32"/>
+      <c r="O11" s="33"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="34" t="s">
+      <c r="B12" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="35"/>
-      <c r="D12" s="32">
+      <c r="C12" s="40"/>
+      <c r="D12" s="43">
         <f>MIN(H4:H8)</f>
         <v>845000</v>
       </c>
-      <c r="E12" s="33"/>
+      <c r="E12" s="44"/>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="17"/>
@@ -1260,23 +1274,24 @@
         <f t="shared" ref="L12:L15" si="7">D5-M5</f>
         <v>90</v>
       </c>
-      <c r="M12" s="42">
+      <c r="M12" s="32">
         <f t="shared" ref="M12:M15" si="8">F5*M5</f>
         <v>112500</v>
       </c>
-      <c r="N12" s="43"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N12" s="32"/>
+      <c r="O12" s="33"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="36" t="s">
+      <c r="B13" s="45" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="36"/>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" s="37"/>
-      <c r="G13" s="37"/>
-      <c r="H13" s="37"/>
+      <c r="C13" s="45"/>
+      <c r="D13" s="45"/>
+      <c r="E13" s="45"/>
+      <c r="F13" s="46"/>
+      <c r="G13" s="46"/>
+      <c r="H13" s="46"/>
       <c r="I13" s="1"/>
       <c r="K13" s="15" t="s">
         <v>3</v>
@@ -1285,20 +1300,21 @@
         <f t="shared" si="7"/>
         <v>83</v>
       </c>
-      <c r="M13" s="42">
+      <c r="M13" s="32">
         <f t="shared" si="8"/>
         <v>244800</v>
       </c>
-      <c r="N13" s="43"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="B14" s="37"/>
-      <c r="C14" s="37"/>
-      <c r="D14" s="37"/>
-      <c r="E14" s="37"/>
-      <c r="F14" s="37"/>
-      <c r="G14" s="37"/>
-      <c r="H14" s="37"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="33"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="B14" s="46"/>
+      <c r="C14" s="46"/>
+      <c r="D14" s="46"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="46"/>
+      <c r="G14" s="46"/>
+      <c r="H14" s="46"/>
       <c r="K14" s="15" t="s">
         <v>4</v>
       </c>
@@ -1306,13 +1322,14 @@
         <f t="shared" si="7"/>
         <v>86</v>
       </c>
-      <c r="M14" s="42">
+      <c r="M14" s="32">
         <f t="shared" si="8"/>
         <v>118300</v>
       </c>
-      <c r="N14" s="43"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="N14" s="32"/>
+      <c r="O14" s="33"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
       <c r="K15" s="15" t="s">
         <v>5</v>
       </c>
@@ -1320,46 +1337,51 @@
         <f t="shared" si="7"/>
         <v>100</v>
       </c>
-      <c r="M15" s="42">
+      <c r="M15" s="32">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="N15" s="43"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E16" s="40" t="s">
+      <c r="N15" s="32"/>
+      <c r="O15" s="33"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="E16" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="38" t="s">
+      <c r="F16" s="49"/>
+      <c r="G16" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="39"/>
-      <c r="I16" s="39"/>
-      <c r="J16" s="39"/>
+      <c r="H16" s="48"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="48"/>
     </row>
   </sheetData>
+  <autoFilter ref="K10:O16">
+    <filterColumn colId="2" showButton="0"/>
+    <filterColumn colId="3" showButton="0"/>
+  </autoFilter>
   <mergeCells count="20">
-    <mergeCell ref="M14:N14"/>
-    <mergeCell ref="M15:N15"/>
-    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="G16:J16"/>
+    <mergeCell ref="E16:F16"/>
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="J2:L2"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="M12:O12"/>
+    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="D11:E11"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="D12:E12"/>
+    <mergeCell ref="B13:H14"/>
+    <mergeCell ref="M14:O14"/>
+    <mergeCell ref="M15:O15"/>
+    <mergeCell ref="J8:P8"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D9:E9"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="D10:E10"/>
-    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="M10:O10"/>
     <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="J2:L2"/>
-    <mergeCell ref="M11:N11"/>
-    <mergeCell ref="M12:N12"/>
-    <mergeCell ref="M13:N13"/>
-    <mergeCell ref="D11:E11"/>
-    <mergeCell ref="B12:C12"/>
-    <mergeCell ref="D12:E12"/>
-    <mergeCell ref="B13:H14"/>
-    <mergeCell ref="G16:J16"/>
-    <mergeCell ref="E16:F16"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="G16" r:id="rId1"/>

--- a/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 3.xlsx
+++ b/exercise/Admin/Admin Keuangan/Tes Excel Admin Keuangan 3.xlsx
@@ -1,23 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="26026"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Pemrograman\Excel\excel\exercise\Admin\Admin Keuangan\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Downloads\Tes Excel Admin Keuangan 3\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B1AE70F-8765-4829-9378-D9498C47A2E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Soal" sheetId="9" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Soal!$K$10:$O$16</definedName>
-  </definedNames>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
@@ -139,7 +137,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
   </numFmts>
@@ -262,7 +260,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -340,26 +338,13 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -405,31 +390,13 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -454,28 +421,25 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="41" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -590,6 +554,23 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri" panose="020F0502020204030204"/>
@@ -625,6 +606,23 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -800,11 +798,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{868AE351-5EAC-4760-9262-7B6887FEAB8D}">
   <sheetPr>
     <tabColor theme="0"/>
   </sheetPr>
-  <dimension ref="A1:Q16"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.42578125" style="11" customWidth="1"/>
@@ -817,22 +815,22 @@
     <col min="10" max="10" width="4.85546875" style="11" customWidth="1"/>
     <col min="11" max="11" width="9.7109375" style="11" customWidth="1"/>
     <col min="12" max="12" width="11.42578125" style="11" customWidth="1"/>
-    <col min="13" max="14" width="9" style="11" customWidth="1"/>
-    <col min="15" max="15" width="16" style="11" customWidth="1"/>
-    <col min="16" max="16" width="13.7109375" style="11" customWidth="1"/>
-    <col min="17" max="17" width="17.140625" style="11" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="11"/>
+    <col min="13" max="13" width="9" style="11" customWidth="1"/>
+    <col min="14" max="14" width="16" style="11" customWidth="1"/>
+    <col min="15" max="15" width="13.7109375" style="11" customWidth="1"/>
+    <col min="16" max="16" width="17.140625" style="11" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="11"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="1"/>
@@ -843,32 +841,30 @@
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
       <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="35" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="42"/>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="29"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="1"/>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="J2" s="42" t="s">
+      <c r="J2" s="35" t="s">
         <v>24</v>
       </c>
-      <c r="K2" s="42"/>
-      <c r="L2" s="42"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
       <c r="O2" s="1"/>
       <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-    </row>
-    <row r="3" spans="1:17" ht="33" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:16" ht="33" x14ac:dyDescent="0.3">
       <c r="A3" s="1"/>
       <c r="B3" s="3" t="s">
         <v>28</v>
@@ -904,18 +900,17 @@
       <c r="M3" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="N3" s="4"/>
+      <c r="N3" s="4" t="s">
+        <v>12</v>
+      </c>
       <c r="O3" s="4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="P3" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="Q3" s="4" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="6" t="s">
         <v>1</v>
@@ -929,18 +924,9 @@
       <c r="E4" s="8">
         <v>85000</v>
       </c>
-      <c r="F4" s="30">
-        <f>C4*E4</f>
-        <v>8500</v>
-      </c>
-      <c r="G4" s="22">
-        <f>E4+F4</f>
-        <v>93500</v>
-      </c>
-      <c r="H4" s="22">
-        <f>F4*D4</f>
-        <v>850000</v>
-      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
       <c r="I4" s="1"/>
       <c r="J4" s="5">
         <v>1</v>
@@ -948,53 +934,31 @@
       <c r="K4" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="L4" s="10">
-        <f>VLOOKUP(K4,$B$3:$H$8,6,FALSE)</f>
-        <v>93500</v>
-      </c>
+      <c r="L4" s="10"/>
       <c r="M4" s="9">
         <v>11</v>
       </c>
-      <c r="N4" s="9"/>
-      <c r="O4" s="10">
-        <f>L4*M4</f>
-        <v>1028500</v>
-      </c>
-      <c r="P4" s="10">
-        <f>IF(M4&gt;10,O4*0.025,0)</f>
-        <v>25712.5</v>
-      </c>
-      <c r="Q4" s="10">
-        <f>O4-P4</f>
-        <v>1002787.5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N4" s="10"/>
+      <c r="O4" s="10"/>
+      <c r="P4" s="10"/>
+    </row>
+    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="25">
+      <c r="C5" s="7">
         <v>0.15</v>
       </c>
-      <c r="D5" s="26">
+      <c r="D5" s="5">
         <v>100</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="8">
         <v>75000</v>
       </c>
-      <c r="F5" s="31">
-        <f t="shared" ref="F5:F8" si="0">C5*E5</f>
-        <v>11250</v>
-      </c>
-      <c r="G5" s="22">
-        <f t="shared" ref="G5:G8" si="1">E5+F5</f>
-        <v>86250</v>
-      </c>
-      <c r="H5" s="22">
-        <f t="shared" ref="H5:H8" si="2">F5*D5</f>
-        <v>1125000</v>
-      </c>
+      <c r="F5" s="22"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
       <c r="I5" s="1"/>
       <c r="J5" s="5">
         <v>2</v>
@@ -1002,28 +966,15 @@
       <c r="K5" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="L5" s="10">
-        <f t="shared" ref="L5:L7" si="3">VLOOKUP(K5,$B$3:$H$8,6,FALSE)</f>
-        <v>86250</v>
-      </c>
+      <c r="L5" s="10"/>
       <c r="M5" s="9">
         <v>10</v>
       </c>
-      <c r="N5" s="9"/>
-      <c r="O5" s="10">
-        <f t="shared" ref="O5:O7" si="4">L5*M5</f>
-        <v>862500</v>
-      </c>
-      <c r="P5" s="10">
-        <f t="shared" ref="P5:P7" si="5">IF(M5&gt;10,O5*0.025,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q5" s="10">
-        <f t="shared" ref="Q5:Q7" si="6">O5-P5</f>
-        <v>862500</v>
-      </c>
-    </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N5" s="10"/>
+      <c r="O5" s="10"/>
+      <c r="P5" s="10"/>
+    </row>
+    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="6" t="s">
         <v>3</v>
@@ -1037,18 +988,9 @@
       <c r="E6" s="8">
         <v>120000</v>
       </c>
-      <c r="F6" s="31">
-        <f t="shared" si="0"/>
-        <v>14400</v>
-      </c>
-      <c r="G6" s="22">
-        <f t="shared" si="1"/>
-        <v>134400</v>
-      </c>
-      <c r="H6" s="22">
-        <f t="shared" si="2"/>
-        <v>1440000</v>
-      </c>
+      <c r="F6" s="22"/>
+      <c r="G6" s="19"/>
+      <c r="H6" s="19"/>
       <c r="I6" s="1"/>
       <c r="J6" s="5">
         <v>3</v>
@@ -1056,28 +998,15 @@
       <c r="K6" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="L6" s="10">
-        <f t="shared" si="3"/>
-        <v>134400</v>
-      </c>
+      <c r="L6" s="10"/>
       <c r="M6" s="9">
         <v>17</v>
       </c>
-      <c r="N6" s="9"/>
-      <c r="O6" s="10">
-        <f t="shared" si="4"/>
-        <v>2284800</v>
-      </c>
-      <c r="P6" s="10">
-        <f t="shared" si="5"/>
-        <v>57120</v>
-      </c>
-      <c r="Q6" s="10">
-        <f t="shared" si="6"/>
-        <v>2227680</v>
-      </c>
-    </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N6" s="10"/>
+      <c r="O6" s="10"/>
+      <c r="P6" s="10"/>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="6" t="s">
         <v>4</v>
@@ -1091,18 +1020,9 @@
       <c r="E7" s="8">
         <v>65000</v>
       </c>
-      <c r="F7" s="31">
-        <f t="shared" si="0"/>
-        <v>8450</v>
-      </c>
-      <c r="G7" s="22">
-        <f t="shared" si="1"/>
-        <v>73450</v>
-      </c>
-      <c r="H7" s="22">
-        <f t="shared" si="2"/>
-        <v>845000</v>
-      </c>
+      <c r="F7" s="22"/>
+      <c r="G7" s="19"/>
+      <c r="H7" s="19"/>
       <c r="I7" s="1"/>
       <c r="J7" s="5">
         <v>4</v>
@@ -1110,28 +1030,15 @@
       <c r="K7" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="L7" s="10">
-        <f t="shared" si="3"/>
-        <v>73450</v>
-      </c>
+      <c r="L7" s="10"/>
       <c r="M7" s="9">
         <v>14</v>
       </c>
-      <c r="N7" s="9"/>
-      <c r="O7" s="10">
-        <f t="shared" si="4"/>
-        <v>1028300</v>
-      </c>
-      <c r="P7" s="10">
-        <f t="shared" si="5"/>
-        <v>25707.5</v>
-      </c>
-      <c r="Q7" s="10">
-        <f t="shared" si="6"/>
-        <v>1002592.5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="N7" s="10"/>
+      <c r="O7" s="10"/>
+      <c r="P7" s="10"/>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="6" t="s">
         <v>5</v>
@@ -1145,65 +1052,45 @@
       <c r="E8" s="8">
         <v>84500</v>
       </c>
-      <c r="F8" s="23">
-        <f t="shared" si="0"/>
-        <v>8450</v>
-      </c>
-      <c r="G8" s="22">
-        <f t="shared" si="1"/>
-        <v>92950</v>
-      </c>
-      <c r="H8" s="22">
-        <f t="shared" si="2"/>
-        <v>845000</v>
-      </c>
+      <c r="F8" s="22"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
       <c r="I8" s="1"/>
-      <c r="J8" s="34" t="s">
+      <c r="J8" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="35"/>
-      <c r="L8" s="35"/>
-      <c r="M8" s="35"/>
-      <c r="N8" s="35"/>
-      <c r="O8" s="35"/>
-      <c r="P8" s="36"/>
-      <c r="Q8" s="20">
-        <f>SUM(Q4:Q7)</f>
-        <v>5095560</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="K8" s="25"/>
+      <c r="L8" s="25"/>
+      <c r="M8" s="25"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="20"/>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
-      <c r="B9" s="37" t="s">
+      <c r="B9" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="32">
-        <f>SUM(H4:H8)</f>
-        <v>5105000</v>
-      </c>
-      <c r="E9" s="33"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
       <c r="I9" s="1"/>
       <c r="J9" s="12"/>
       <c r="K9" s="12"/>
       <c r="L9" s="12"/>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
-      <c r="O9" s="13"/>
-      <c r="P9" s="12"/>
-      <c r="Q9" s="14"/>
-    </row>
-    <row r="10" spans="1:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O9" s="12"/>
+      <c r="P9" s="14"/>
+    </row>
+    <row r="10" spans="1:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="39" t="s">
+      <c r="B10" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="32">
-        <f>AVERAGE(H4:H8)</f>
-        <v>1021000</v>
-      </c>
-      <c r="E10" s="33"/>
+      <c r="C10" s="30"/>
+      <c r="D10" s="23"/>
+      <c r="E10" s="23"/>
       <c r="F10" s="17"/>
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
@@ -1215,25 +1102,21 @@
       <c r="L10" s="16" t="s">
         <v>23</v>
       </c>
-      <c r="M10" s="41" t="s">
+      <c r="M10" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="N10" s="41"/>
-      <c r="O10" s="41"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="1"/>
       <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
-      <c r="B11" s="39" t="s">
+      <c r="B11" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="43">
-        <f>MAX(H4:H8)</f>
-        <v>1440000</v>
-      </c>
-      <c r="E11" s="44"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="32"/>
       <c r="F11" s="18"/>
       <c r="G11" s="18"/>
       <c r="H11" s="17"/>
@@ -1241,28 +1124,18 @@
       <c r="K11" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="L11" s="19">
-        <f>D4-M4</f>
-        <v>89</v>
-      </c>
-      <c r="M11" s="32">
-        <f>F4*M4</f>
-        <v>93500</v>
-      </c>
-      <c r="N11" s="32"/>
-      <c r="O11" s="33"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L11" s="19"/>
+      <c r="M11" s="23"/>
+      <c r="N11" s="23"/>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
-      <c r="B12" s="39" t="s">
+      <c r="B12" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="43">
-        <f>MIN(H4:H8)</f>
-        <v>845000</v>
-      </c>
-      <c r="E12" s="44"/>
+      <c r="C12" s="30"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
       <c r="F12" s="18"/>
       <c r="G12" s="18"/>
       <c r="H12" s="17"/>
@@ -1270,121 +1143,89 @@
       <c r="K12" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="L12" s="21">
-        <f t="shared" ref="L12:L15" si="7">D5-M5</f>
-        <v>90</v>
-      </c>
-      <c r="M12" s="32">
-        <f t="shared" ref="M12:M15" si="8">F5*M5</f>
-        <v>112500</v>
-      </c>
-      <c r="N12" s="32"/>
-      <c r="O12" s="33"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L12" s="19"/>
+      <c r="M12" s="23"/>
+      <c r="N12" s="23"/>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
-      <c r="B13" s="45" t="s">
+      <c r="B13" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="C13" s="45"/>
-      <c r="D13" s="45"/>
-      <c r="E13" s="45"/>
-      <c r="F13" s="46"/>
-      <c r="G13" s="46"/>
-      <c r="H13" s="46"/>
+      <c r="C13" s="33"/>
+      <c r="D13" s="33"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="34"/>
+      <c r="G13" s="34"/>
+      <c r="H13" s="34"/>
       <c r="I13" s="1"/>
       <c r="K13" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="L13" s="21">
-        <f t="shared" si="7"/>
-        <v>83</v>
-      </c>
-      <c r="M13" s="32">
-        <f t="shared" si="8"/>
-        <v>244800</v>
-      </c>
-      <c r="N13" s="32"/>
-      <c r="O13" s="33"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="B14" s="46"/>
-      <c r="C14" s="46"/>
-      <c r="D14" s="46"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="46"/>
-      <c r="G14" s="46"/>
-      <c r="H14" s="46"/>
+      <c r="L13" s="19"/>
+      <c r="M13" s="23"/>
+      <c r="N13" s="23"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="B14" s="34"/>
+      <c r="C14" s="34"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="34"/>
+      <c r="F14" s="34"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="34"/>
       <c r="K14" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="L14" s="21">
-        <f t="shared" si="7"/>
-        <v>86</v>
-      </c>
-      <c r="M14" s="32">
-        <f t="shared" si="8"/>
-        <v>118300</v>
-      </c>
-      <c r="N14" s="32"/>
-      <c r="O14" s="33"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="L14" s="19"/>
+      <c r="M14" s="23"/>
+      <c r="N14" s="23"/>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
       <c r="K15" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="L15" s="21">
-        <f t="shared" si="7"/>
-        <v>100</v>
-      </c>
-      <c r="M15" s="32">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="32"/>
-      <c r="O15" s="33"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.3">
-      <c r="E16" s="49" t="s">
+      <c r="L15" s="19"/>
+      <c r="M15" s="23"/>
+      <c r="N15" s="23"/>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="E16" s="36" t="s">
         <v>31</v>
       </c>
-      <c r="F16" s="49"/>
-      <c r="G16" s="47" t="s">
+      <c r="F16" s="36"/>
+      <c r="G16" s="37" t="s">
         <v>30</v>
       </c>
-      <c r="H16" s="48"/>
-      <c r="I16" s="48"/>
-      <c r="J16" s="48"/>
+      <c r="H16" s="38"/>
+      <c r="I16" s="38"/>
+      <c r="J16" s="38"/>
     </row>
   </sheetData>
-  <autoFilter ref="K10:O16">
-    <filterColumn colId="2" showButton="0"/>
-    <filterColumn colId="3" showButton="0"/>
-  </autoFilter>
   <mergeCells count="20">
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="E16:F16"/>
     <mergeCell ref="B2:E2"/>
     <mergeCell ref="J2:L2"/>
-    <mergeCell ref="M11:O11"/>
-    <mergeCell ref="M12:O12"/>
-    <mergeCell ref="M13:O13"/>
+    <mergeCell ref="M11:N11"/>
+    <mergeCell ref="M12:N12"/>
+    <mergeCell ref="M13:N13"/>
+    <mergeCell ref="M14:N14"/>
+    <mergeCell ref="M15:N15"/>
+    <mergeCell ref="J8:O8"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="D9:E9"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:E10"/>
+    <mergeCell ref="M10:N10"/>
+    <mergeCell ref="B11:C11"/>
     <mergeCell ref="D11:E11"/>
     <mergeCell ref="B12:C12"/>
     <mergeCell ref="D12:E12"/>
     <mergeCell ref="B13:H14"/>
-    <mergeCell ref="M14:O14"/>
-    <mergeCell ref="M15:O15"/>
-    <mergeCell ref="J8:P8"/>
-    <mergeCell ref="B9:C9"/>
-    <mergeCell ref="D9:E9"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:E10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="G16" r:id="rId1"/>
+    <hyperlink ref="G16" r:id="rId1" xr:uid="{209A80AC-3FCB-45C1-B278-3C422403E500}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId2"/>
